--- a/Transactional-data.xlsx
+++ b/Transactional-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\0WorkingOn\Sonny-DAX\Module2 Data Analysis Expression(DAX)\Project2Majestic Traders Kings of Import and Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9385F5BF-BB1D-46FF-97BC-5F7A3D74E9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7B9EC3-4D41-49AD-A684-71F7BF54DB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="1104" windowWidth="24156" windowHeight="15396" xr2:uid="{415AA908-4F29-43D7-A425-5F36B6D9A4DD}"/>
+    <workbookView xWindow="4116" yWindow="1596" windowWidth="24000" windowHeight="13272" activeTab="1" xr2:uid="{415AA908-4F29-43D7-A425-5F36B6D9A4DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -38903,9 +38903,7 @@
       <c r="D27" s="2">
         <v>21</v>
       </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
@@ -39634,9 +39632,7 @@
       <c r="D70" s="2">
         <v>40</v>
       </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
+      <c r="E70" s="1"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
@@ -40688,9 +40684,7 @@
       <c r="D132" s="2">
         <v>4</v>
       </c>
-      <c r="E132" s="1">
-        <v>0</v>
-      </c>
+      <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
@@ -40705,9 +40699,7 @@
       <c r="D133" s="2">
         <v>24</v>
       </c>
-      <c r="E133" s="1">
-        <v>0</v>
-      </c>
+      <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
@@ -40722,9 +40714,7 @@
       <c r="D134" s="2">
         <v>12</v>
       </c>
-      <c r="E134" s="1">
-        <v>0</v>
-      </c>
+      <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
@@ -40739,9 +40729,7 @@
       <c r="D135" s="2">
         <v>14</v>
       </c>
-      <c r="E135" s="1">
-        <v>0</v>
-      </c>
+      <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
@@ -40756,9 +40744,7 @@
       <c r="D136" s="2">
         <v>70</v>
       </c>
-      <c r="E136" s="1">
-        <v>0</v>
-      </c>
+      <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
@@ -40773,9 +40759,7 @@
       <c r="D137" s="2">
         <v>6</v>
       </c>
-      <c r="E137" s="1">
-        <v>0</v>
-      </c>
+      <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
@@ -40790,9 +40774,7 @@
       <c r="D138" s="2">
         <v>8</v>
       </c>
-      <c r="E138" s="1">
-        <v>0</v>
-      </c>
+      <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
@@ -40807,9 +40789,7 @@
       <c r="D139" s="2">
         <v>14</v>
       </c>
-      <c r="E139" s="1">
-        <v>0</v>
-      </c>
+      <c r="E139" s="1"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
@@ -40824,9 +40804,7 @@
       <c r="D140" s="2">
         <v>5</v>
       </c>
-      <c r="E140" s="1">
-        <v>0</v>
-      </c>
+      <c r="E140" s="1"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
@@ -40841,9 +40819,7 @@
       <c r="D141" s="2">
         <v>4</v>
       </c>
-      <c r="E141" s="1">
-        <v>0</v>
-      </c>
+      <c r="E141" s="1"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
@@ -40858,9 +40834,7 @@
       <c r="D142" s="2">
         <v>4</v>
       </c>
-      <c r="E142" s="1">
-        <v>0</v>
-      </c>
+      <c r="E142" s="1"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
@@ -40875,9 +40849,7 @@
       <c r="D143" s="2">
         <v>6</v>
       </c>
-      <c r="E143" s="1">
-        <v>0</v>
-      </c>
+      <c r="E143" s="1"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
@@ -40892,9 +40864,7 @@
       <c r="D144" s="2">
         <v>12</v>
       </c>
-      <c r="E144" s="1">
-        <v>0</v>
-      </c>
+      <c r="E144" s="1"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
@@ -40909,9 +40879,7 @@
       <c r="D145" s="2">
         <v>9</v>
       </c>
-      <c r="E145" s="1">
-        <v>0</v>
-      </c>
+      <c r="E145" s="1"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
@@ -42252,9 +42220,7 @@
       <c r="D224" s="2">
         <v>12</v>
       </c>
-      <c r="E224" s="1">
-        <v>0</v>
-      </c>
+      <c r="E224" s="1"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
@@ -42269,9 +42235,7 @@
       <c r="D225" s="2">
         <v>49</v>
       </c>
-      <c r="E225" s="1">
-        <v>0</v>
-      </c>
+      <c r="E225" s="1"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
@@ -42286,9 +42250,7 @@
       <c r="D226" s="2">
         <v>16</v>
       </c>
-      <c r="E226" s="1">
-        <v>0</v>
-      </c>
+      <c r="E226" s="1"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
